--- a/results/scenario_base_case/electricity_price.xlsx
+++ b/results/scenario_base_case/electricity_price.xlsx
@@ -15281,7 +15281,7 @@
     <row r="1346">
       <c r="A1346" s="1" t="inlineStr">
         <is>
-          <t>rp08</t>
+          <t>rp_design</t>
         </is>
       </c>
       <c r="B1346" s="1" t="inlineStr">
